--- a/working-example/DGF.xlsx
+++ b/working-example/DGF.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t xml:space="preserve">desired_data_class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desired_data_format</t>
   </si>
   <si>
     <t xml:space="preserve">rg_properties</t>
@@ -2263,6 +2266,9 @@
   </si>
   <si>
     <t xml:space="preserve">geography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code</t>
   </si>
   <si>
     <t xml:space="preserve">20190 ;; 20189 ;; 20180 ;; 20199 ;; 20179 ;; 20170 ;; 20169 ;; 20191 ;; 20200 ;; 20181 ;; 20171 ;; 20201</t>
@@ -4364,6 +4370,7 @@
     <col min="25" max="25" width="20.71" hidden="0" customWidth="1"/>
     <col min="26" max="26" width="20.71" hidden="0" customWidth="1"/>
     <col min="27" max="27" width="20.71" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -4448,64 +4455,67 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="T2" s="7" t="s">
         <v>33</v>
@@ -4516,79 +4526,82 @@
       <c r="V2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="W2" s="7" t="n">
+      <c r="W2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2" s="7" t="n">
         <v>97</v>
       </c>
-      <c r="X2" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y2" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z2" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA2" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J3" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="T3" s="7" t="s">
         <v>40</v>
@@ -4599,79 +4612,82 @@
       <c r="V3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="W3" s="7" t="n">
+      <c r="W3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="X3" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y3" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z3" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA3" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J4" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S4" s="6" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="T4" s="7" t="s">
         <v>47</v>
@@ -4682,79 +4698,82 @@
       <c r="V4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="W4" s="7" t="n">
+      <c r="W4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="X4" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="X4" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y4" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z4" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA4" s="7" t="s">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J5" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="T5" s="7" t="s">
         <v>54</v>
@@ -4765,79 +4784,82 @@
       <c r="V5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="W5" s="7" t="n">
+      <c r="W5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="X5" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="X5" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y5" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>57</v>
+        <v>29</v>
+      </c>
+      <c r="AB5" s="7" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J6" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="T6" s="7" t="s">
         <v>63</v>
@@ -4846,81 +4868,84 @@
         <v>64</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="W6" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="X6" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="X6" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y6" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z6" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA6" s="7" t="s">
-        <v>65</v>
+        <v>29</v>
+      </c>
+      <c r="AB6" s="7" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J7" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O7" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q7" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S7" s="6" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="T7" s="7" t="s">
         <v>72</v>
@@ -4931,79 +4956,82 @@
       <c r="V7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="W7" s="7" t="n">
+      <c r="W7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="X7" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="X7" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y7" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA7" s="7" t="s">
-        <v>75</v>
+        <v>29</v>
+      </c>
+      <c r="AB7" s="7" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J8" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="T8" s="7" t="s">
         <v>80</v>
@@ -5014,79 +5042,82 @@
       <c r="V8" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="W8" s="7" t="n">
+      <c r="W8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="X8" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="X8" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y8" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA8" s="7" t="s">
-        <v>83</v>
+        <v>29</v>
+      </c>
+      <c r="AB8" s="7" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O9" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q9" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="T9" s="7" t="s">
         <v>88</v>
@@ -5097,79 +5128,82 @@
       <c r="V9" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="W9" s="7" t="n">
+      <c r="W9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="X9" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="X9" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y9" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA9" s="7" t="s">
-        <v>91</v>
+        <v>29</v>
+      </c>
+      <c r="AB9" s="7" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J10" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O10" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q10" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="T10" s="7" t="s">
         <v>96</v>
@@ -5180,79 +5214,82 @@
       <c r="V10" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="W10" s="7" t="n">
+      <c r="W10" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="X10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="X10" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y10" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA10" s="7" t="s">
-        <v>99</v>
+        <v>29</v>
+      </c>
+      <c r="AB10" s="7" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J11" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q11" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="T11" s="7" t="s">
         <v>103</v>
@@ -5263,79 +5300,82 @@
       <c r="V11" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="W11" s="7" t="n">
+      <c r="W11" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="X11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="X11" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>106</v>
+        <v>29</v>
+      </c>
+      <c r="AB11" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J12" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q12" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="T12" s="7" t="s">
         <v>111</v>
@@ -5346,79 +5386,82 @@
       <c r="V12" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="W12" s="7" t="n">
+      <c r="W12" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="X12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="X12" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y12" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z12" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA12" s="7" t="s">
-        <v>114</v>
+        <v>29</v>
+      </c>
+      <c r="AB12" s="7" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J13" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="T13" s="7" t="s">
         <v>119</v>
@@ -5429,79 +5472,82 @@
       <c r="V13" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="W13" s="7" t="n">
+      <c r="W13" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="X13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="X13" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y13" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>122</v>
+        <v>29</v>
+      </c>
+      <c r="AB13" s="7" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J14" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q14" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="T14" s="7" t="s">
         <v>127</v>
@@ -5512,79 +5558,82 @@
       <c r="V14" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="W14" s="7" t="n">
+      <c r="W14" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="X14" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="X14" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y14" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z14" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA14" s="7" t="s">
-        <v>130</v>
+        <v>29</v>
+      </c>
+      <c r="AB14" s="7" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J15" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q15" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="T15" s="7" t="s">
         <v>136</v>
@@ -5595,79 +5644,82 @@
       <c r="V15" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="W15" s="7" t="n">
+      <c r="W15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="X15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="X15" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y15" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA15" s="7" t="s">
-        <v>139</v>
+        <v>29</v>
+      </c>
+      <c r="AB15" s="7" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J16" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q16" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="T16" s="7" t="s">
         <v>144</v>
@@ -5678,79 +5730,82 @@
       <c r="V16" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="W16" s="7" t="n">
+      <c r="W16" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="X16" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="X16" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y16" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z16" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA16" s="7" t="s">
-        <v>147</v>
+        <v>29</v>
+      </c>
+      <c r="AB16" s="7" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J17" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="T17" s="7" t="s">
         <v>151</v>
@@ -5759,81 +5814,84 @@
         <v>152</v>
       </c>
       <c r="V17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="W17" s="7" t="n">
+        <v>153</v>
+      </c>
+      <c r="W17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="X17" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="X17" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y17" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z17" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA17" s="7" t="s">
-        <v>153</v>
+        <v>29</v>
+      </c>
+      <c r="AB17" s="7" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J18" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="T18" s="7" t="s">
         <v>157</v>
@@ -5844,79 +5902,82 @@
       <c r="V18" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="W18" s="7" t="n">
+      <c r="W18" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="X18" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="X18" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y18" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z18" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA18" s="7" t="s">
-        <v>160</v>
+        <v>29</v>
+      </c>
+      <c r="AB18" s="7" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J19" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>164</v>
+        <v>29</v>
       </c>
       <c r="T19" s="7" t="s">
         <v>165</v>
@@ -5927,79 +5988,82 @@
       <c r="V19" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="W19" s="7" t="n">
+      <c r="W19" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="X19" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="X19" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y19" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z19" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA19" s="7" t="s">
-        <v>168</v>
+        <v>29</v>
+      </c>
+      <c r="AB19" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J20" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>172</v>
+        <v>29</v>
       </c>
       <c r="T20" s="7" t="s">
         <v>173</v>
@@ -6010,684 +6074,711 @@
       <c r="V20" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="W20" s="7" t="n">
+      <c r="W20" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="X20" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="X20" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y20" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z20" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA20" s="7" t="s">
-        <v>176</v>
+        <v>29</v>
+      </c>
+      <c r="AB20" s="7" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J21" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>182</v>
+        <v>88</v>
       </c>
       <c r="U21" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="V21" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="W21" s="7" t="n">
+        <v>185</v>
+      </c>
+      <c r="W21" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="X21" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="X21" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y21" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z21" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA21" s="7" t="s">
-        <v>185</v>
+        <v>29</v>
+      </c>
+      <c r="AB21" s="7" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="J22" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q22" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S22" s="6" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>189</v>
+        <v>88</v>
       </c>
       <c r="U22" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="V22" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="W22" s="7" t="n">
+        <v>192</v>
+      </c>
+      <c r="W22" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="X22" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="X22" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y22" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z22" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA22" s="7" t="s">
-        <v>192</v>
+        <v>29</v>
+      </c>
+      <c r="AB22" s="7" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J23" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q23" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S23" s="6" t="s">
-        <v>195</v>
+        <v>29</v>
       </c>
       <c r="T23" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="U23" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="V23" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="W23" s="7" t="n">
+        <v>199</v>
+      </c>
+      <c r="W23" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="X23" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="X23" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y23" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z23" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA23" s="7" t="s">
-        <v>199</v>
+        <v>29</v>
+      </c>
+      <c r="AB23" s="7" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J24" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q24" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S24" s="6" t="s">
-        <v>202</v>
+        <v>29</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V24" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="W24" s="7" t="n">
+        <v>206</v>
+      </c>
+      <c r="W24" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="X24" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="X24" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y24" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z24" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA24" s="7" t="s">
-        <v>206</v>
+        <v>29</v>
+      </c>
+      <c r="AB24" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J25" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N25" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q25" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>209</v>
+        <v>29</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="W25" s="7" t="n">
+        <v>213</v>
+      </c>
+      <c r="W25" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="X25" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="X25" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y25" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z25" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA25" s="7" t="s">
-        <v>213</v>
+        <v>29</v>
+      </c>
+      <c r="AB25" s="7" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J26" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q26" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S26" s="6" t="s">
-        <v>216</v>
+        <v>29</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U26" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="V26" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="W26" s="7" t="n">
+        <v>220</v>
+      </c>
+      <c r="W26" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="X26" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="X26" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y26" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z26" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA26" s="7" t="s">
-        <v>220</v>
+        <v>29</v>
+      </c>
+      <c r="AB26" s="7" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J27" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q27" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S27" s="6" t="s">
-        <v>223</v>
+        <v>29</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="U27" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="V27" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="W27" s="7" t="n">
+        <v>227</v>
+      </c>
+      <c r="W27" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="X27" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="X27" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y27" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z27" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA27" s="7" t="s">
-        <v>227</v>
+        <v>29</v>
+      </c>
+      <c r="AB27" s="7" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J28" s="9" t="b">
         <v>0</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q28" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S28" s="6" t="s">
-        <v>230</v>
+        <v>29</v>
       </c>
       <c r="T28" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="U28" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="V28" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="W28" s="7" t="n">
+        <v>234</v>
+      </c>
+      <c r="W28" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="X28" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="X28" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="Y28" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z28" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA28" s="7" t="s">
-        <v>234</v>
+        <v>29</v>
+      </c>
+      <c r="AB28" s="7" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/working-example/DGF.xlsx
+++ b/working-example/DGF.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="244">
   <si>
     <t xml:space="preserve">var_name</t>
   </si>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">EIN</t>
   </si>
   <si>
-    <t xml:space="preserve">numeric</t>
+    <t xml:space="preserve">TRUE</t>
   </si>
   <si>
     <t xml:space="preserve">113161527 ;; 
@@ -672,7 +672,19 @@
 542015951</t>
   </si>
   <si>
+    <t xml:space="preserve">numeric</t>
+  </si>
+  <si>
     <t xml:space="preserve">identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">numeric_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">administrative_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plain</t>
   </si>
   <si>
     <t xml:space="preserve">[ 
@@ -1649,6 +1661,9 @@
 36001</t>
   </si>
   <si>
+    <t xml:space="preserve">geographic_id</t>
+  </si>
+  <si>
     <t xml:space="preserve">[ 
   {  "STAT" :  "Rows"  ,  "VAL" :  "25,000"  ,  "PER" :  ""  }, 
   {  "STAT" :  "Distinct"  ,  "VAL" :  "2,411"  ,  "PER" :  "(9.6%)"  }, 
@@ -2026,6 +2041,18 @@
 201905</t>
   </si>
   <si>
+    <t xml:space="preserve">month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temporal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yyyymm</t>
+  </si>
+  <si>
     <t xml:space="preserve">[ 
   {  "STAT" :  "Rows"  ,  "VAL" :  "25,000"  ,  "PER" :  ""  }, 
   {  "STAT" :  "Distinct"  ,  "VAL" :  "47"  ,  "PER" :  "(0.2%)"  }
@@ -2036,65 +2063,53 @@
   </si>
   <si>
     <t xml:space="preserve">[ 
-  {  "Value" :  "201912"  ,  "Frequency" :  9884  }, 
-  {  "Value" :  "201812"  ,  "Frequency" :  3477  }, 
-  {  "Value" :  "201906"  ,  "Frequency" :  2064  }, 
-  {  "Value" :  "201712"  ,  "Frequency" :  1626  }, 
-  {  "Value" :  "202006"  ,  "Frequency" :  1312  }, 
-  {  "Value" :  "201806"  ,  "Frequency" :  840  }, 
-  {  "Value" :  "201909"  ,  "Frequency" :  812  }, 
-  {  "Value" :  "201908"  ,  "Frequency" :  406  }, 
-  {  "Value" :  "201706"  ,  "Frequency" :  362  }, 
-  {  "Value" :  "201903"  ,  "Frequency" :  356  }, 
-  {  "Value" :  "202003"  ,  "Frequency" :  352  }, 
-  {  "Value" :  "201905"  ,  "Frequency" :  326  }, 
-  {  "Value" :  "201904"  ,  "Frequency" :  278  }, 
-  {  "Value" :  "201910"  ,  "Frequency" :  272  }, 
-  {  "Value" :  "202005"  ,  "Frequency" :  252  }, 
-  {  "Value" :  "201809"  ,  "Frequency" :  244  }, 
-  {  "Value" :  "202004"  ,  "Frequency" :  183  }, 
-  {  "Value" :  "201907"  ,  "Frequency" :  161  }, 
-  {  "Value" :  "201805"  ,  "Frequency" :  154  }, 
-  {  "Value" :  "201808"  ,  "Frequency" :  139  }, 
-  {  "Value" :  "201911"  ,  "Frequency" :  123  }, 
-  {  "Value" :  "201709"  ,  "Frequency" :  121  }, 
-  {  "Value" :  "201803"  ,  "Frequency" :  110  }, 
-  {  "Value" :  "201804"  ,  "Frequency" :  102  }, 
-  {  "Value" :  "201810"  ,  "Frequency" :  94  }, 
-  {  "Value" :  "202007"  ,  "Frequency" :  91  }, 
-  {  "Value" :  "202008"  ,  "Frequency" :  79  }, 
-  {  "Value" :  "202009"  ,  "Frequency" :  74  }, 
-  {  "Value" :  "202001"  ,  "Frequency" :  66  }, 
-  {  "Value" :  "201807"  ,  "Frequency" :  65  }, 
-  {  "Value" :  "201705"  ,  "Frequency" :  64  }, 
-  {  "Value" :  "201708"  ,  "Frequency" :  64  }, 
-  {  "Value" :  "202002"  ,  "Frequency" :  59  }, 
-  {  "Value" :  "201902"  ,  "Frequency" :  57  }, 
-  {  "Value" :  "201704"  ,  "Frequency" :  46  }, 
-  {  "Value" :  "201710"  ,  "Frequency" :  46  }, 
-  {  "Value" :  "201811"  ,  "Frequency" :  46  }, 
-  {  "Value" :  "201901"  ,  "Frequency" :  34  }, 
-  {  "Value" :  "201707"  ,  "Frequency" :  32  }, 
-  {  "Value" :  "201802"  ,  "Frequency" :  32  }, 
-  {  "Value" :  "201703"  ,  "Frequency" :  31  }, 
-  {  "Value" :  "201711"  ,  "Frequency" :  25  }, 
-  {  "Value" :  "202010"  ,  "Frequency" :  13  }, 
-  {  "Value" :  "201801"  ,  "Frequency" :  9  }, 
-  {  "Value" :  "201701"  ,  "Frequency" :  8  }, 
-  {  "Value" :  "201702"  ,  "Frequency" :  8  }, 
-  {  "Value" :  "202011"  ,  "Frequency" :  1  }
-]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 
-  {  "x" :  "201912"  ,  "Freq" :  9884  }, 
-  {  "x" :  "201812"  ,  "Freq" :  3477  }, 
-  {  "x" :  "201906"  ,  "Freq" :  2064  }, 
-  {  "x" :  "201712"  ,  "Freq" :  1626  }, 
-  {  "x" :  "202006"  ,  "Freq" :  1312  }, 
-  {  "x" :  "201806"  ,  "Freq" :  840  }, 
-  {  "x" :  "201909"  ,  "Freq" :  812  }, 
-  {  "x" :  "other"  ,  "Freq" :  4985  }
+  {  "Value" :  "201701"  ,  "Count" :  8  }, 
+  {  "Value" :  "201702"  ,  "Count" :  8  }, 
+  {  "Value" :  "201703"  ,  "Count" :  31  }, 
+  {  "Value" :  "201704"  ,  "Count" :  46  }, 
+  {  "Value" :  "201705"  ,  "Count" :  64  }, 
+  {  "Value" :  "201706"  ,  "Count" :  362  }, 
+  {  "Value" :  "201707"  ,  "Count" :  32  }, 
+  {  "Value" :  "201708"  ,  "Count" :  64  }, 
+  {  "Value" :  "201709"  ,  "Count" :  121  }, 
+  {  "Value" :  "201710"  ,  "Count" :  46  }, 
+  {  "Value" :  "201711"  ,  "Count" :  25  }, 
+  {  "Value" :  "201712"  ,  "Count" :  1626  }, 
+  {  "Value" :  "201801"  ,  "Count" :  9  }, 
+  {  "Value" :  "201802"  ,  "Count" :  32  }, 
+  {  "Value" :  "201803"  ,  "Count" :  110  }, 
+  {  "Value" :  "201804"  ,  "Count" :  102  }, 
+  {  "Value" :  "201805"  ,  "Count" :  154  }, 
+  {  "Value" :  "201806"  ,  "Count" :  840  }, 
+  {  "Value" :  "201807"  ,  "Count" :  65  }, 
+  {  "Value" :  "201808"  ,  "Count" :  139  }, 
+  {  "Value" :  "201809"  ,  "Count" :  244  }, 
+  {  "Value" :  "201810"  ,  "Count" :  94  }, 
+  {  "Value" :  "201811"  ,  "Count" :  46  }, 
+  {  "Value" :  "201812"  ,  "Count" :  3477  }, 
+  {  "Value" :  "201901"  ,  "Count" :  34  }, 
+  {  "Value" :  "201902"  ,  "Count" :  57  }, 
+  {  "Value" :  "201903"  ,  "Count" :  356  }, 
+  {  "Value" :  "201904"  ,  "Count" :  278  }, 
+  {  "Value" :  "201905"  ,  "Count" :  326  }, 
+  {  "Value" :  "201906"  ,  "Count" :  2064  }, 
+  {  "Value" :  "201907"  ,  "Count" :  161  }, 
+  {  "Value" :  "201908"  ,  "Count" :  406  }, 
+  {  "Value" :  "201909"  ,  "Count" :  812  }, 
+  {  "Value" :  "201910"  ,  "Count" :  272  }, 
+  {  "Value" :  "201911"  ,  "Count" :  123  }, 
+  {  "Value" :  "201912"  ,  "Count" :  9884  }, 
+  {  "Value" :  "202001"  ,  "Count" :  66  }, 
+  {  "Value" :  "202002"  ,  "Count" :  59  }, 
+  {  "Value" :  "202003"  ,  "Count" :  352  }, 
+  {  "Value" :  "202004"  ,  "Count" :  183  }, 
+  {  "Value" :  "202005"  ,  "Count" :  252  }, 
+  {  "Value" :  "202006"  ,  "Count" :  1312  }, 
+  {  "Value" :  "202007"  ,  "Count" :  91  }, 
+  {  "Value" :  "202008"  ,  "Count" :  79  }, 
+  {  "Value" :  "202009"  ,  "Count" :  74  }, 
+  {  "Value" :  "202010"  ,  "Count" :  13  }, 
+  {  "Value" :  "202011"  ,  "Count" :  1  }
 ]</t>
   </si>
   <si>
@@ -2172,64 +2187,52 @@
   </si>
   <si>
     <t xml:space="preserve">[ 
-  {  "Value" :  "201812"  ,  "Frequency" :  9298  }, 
-  {  "Value" :  "201712"  ,  "Frequency" :  3002  }, 
-  {  "Value" :  "201806"  ,  "Frequency" :  1767  }, 
-  {  "Value" :  "201906"  ,  "Frequency" :  1060  }, 
-  {  "Value" :  "201809"  ,  "Frequency" :  744  }, 
-  {  "Value" :  "201706"  ,  "Frequency" :  539  }, 
-  {  "Value" :  "201612"  ,  "Frequency" :  478  }, 
-  {  "Value" :  "201808"  ,  "Frequency" :  370  }, 
-  {  "Value" :  "201803"  ,  "Frequency" :  321  }, 
-  {  "Value" :  "201903"  ,  "Frequency" :  319  }, 
-  {  "Value" :  "201805"  ,  "Frequency" :  265  }, 
-  {  "Value" :  "201810"  ,  "Frequency" :  255  }, 
-  {  "Value" :  "201804"  ,  "Frequency" :  246  }, 
-  {  "Value" :  "201905"  ,  "Frequency" :  206  }, 
-  {  "Value" :  "201709"  ,  "Frequency" :  195  }, 
-  {  "Value" :  "201606"  ,  "Frequency" :  164  }, 
-  {  "Value" :  "201904"  ,  "Frequency" :  162  }, 
-  {  "Value" :  "201807"  ,  "Frequency" :  123  }, 
-  {  "Value" :  "201811"  ,  "Frequency" :  122  }, 
-  {  "Value" :  "201708"  ,  "Frequency" :  101  }, 
-  {  "Value" :  "201705"  ,  "Frequency" :  90  }, 
-  {  "Value" :  "201710"  ,  "Frequency" :  88  }, 
-  {  "Value" :  "201704"  ,  "Frequency" :  64  }, 
-  {  "Value" :  "201901"  ,  "Frequency" :  61  }, 
-  {  "Value" :  "201907"  ,  "Frequency" :  58  }, 
-  {  "Value" :  "201703"  ,  "Frequency" :  51  }, 
-  {  "Value" :  "201902"  ,  "Frequency" :  49  }, 
-  {  "Value" :  "201802"  ,  "Frequency" :  46  }, 
-  {  "Value" :  "201908"  ,  "Frequency" :  44  }, 
-  {  "Value" :  "201909"  ,  "Frequency" :  42  }, 
-  {  "Value" :  "201711"  ,  "Frequency" :  41  }, 
-  {  "Value" :  "201707"  ,  "Frequency" :  39  }, 
-  {  "Value" :  "201605"  ,  "Frequency" :  36  }, 
-  {  "Value" :  "201609"  ,  "Frequency" :  34  }, 
-  {  "Value" :  "201801"  ,  "Frequency" :  29  }, 
-  {  "Value" :  "201604"  ,  "Frequency" :  27  }, 
-  {  "Value" :  "201608"  ,  "Frequency" :  23  }, 
-  {  "Value" :  "201702"  ,  "Frequency" :  22  }, 
-  {  "Value" :  "201603"  ,  "Frequency" :  18  }, 
-  {  "Value" :  "201607"  ,  "Frequency" :  16  }, 
-  {  "Value" :  "201610"  ,  "Frequency" :  13  }, 
-  {  "Value" :  "201611"  ,  "Frequency" :  9  }, 
-  {  "Value" :  "201910"  ,  "Frequency" :  7  }, 
-  {  "Value" :  "201601"  ,  "Frequency" :  5  }, 
-  {  "Value" :  "201602"  ,  "Frequency" :  4  }, 
-  {  "Value" :  "201701"  ,  "Frequency" :  3  }
-]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[ 
-  {  "x" :  "201812"  ,  "Freq" :  9298  }, 
-  {  "x" :  "201712"  ,  "Freq" :  3002  }, 
-  {  "x" :  "201806"  ,  "Freq" :  1767  }, 
-  {  "x" :  "201906"  ,  "Freq" :  1060  }, 
-  {  "x" :  "201809"  ,  "Freq" :  744  }, 
-  {  "x" :  "201706"  ,  "Freq" :  539  }, 
-  {  "x" :  "201612"  ,  "Freq" :  478  }, 
-  {  "x" :  "other"  ,  "Freq" :  3768  }
+  {  "Value" :  "201601"  ,  "Count" :  5  }, 
+  {  "Value" :  "201602"  ,  "Count" :  4  }, 
+  {  "Value" :  "201603"  ,  "Count" :  18  }, 
+  {  "Value" :  "201604"  ,  "Count" :  27  }, 
+  {  "Value" :  "201605"  ,  "Count" :  36  }, 
+  {  "Value" :  "201606"  ,  "Count" :  164  }, 
+  {  "Value" :  "201607"  ,  "Count" :  16  }, 
+  {  "Value" :  "201608"  ,  "Count" :  23  }, 
+  {  "Value" :  "201609"  ,  "Count" :  34  }, 
+  {  "Value" :  "201610"  ,  "Count" :  13  }, 
+  {  "Value" :  "201611"  ,  "Count" :  9  }, 
+  {  "Value" :  "201612"  ,  "Count" :  478  }, 
+  {  "Value" :  "201701"  ,  "Count" :  3  }, 
+  {  "Value" :  "201702"  ,  "Count" :  22  }, 
+  {  "Value" :  "201703"  ,  "Count" :  51  }, 
+  {  "Value" :  "201704"  ,  "Count" :  64  }, 
+  {  "Value" :  "201705"  ,  "Count" :  90  }, 
+  {  "Value" :  "201706"  ,  "Count" :  539  }, 
+  {  "Value" :  "201707"  ,  "Count" :  39  }, 
+  {  "Value" :  "201708"  ,  "Count" :  101  }, 
+  {  "Value" :  "201709"  ,  "Count" :  195  }, 
+  {  "Value" :  "201710"  ,  "Count" :  88  }, 
+  {  "Value" :  "201711"  ,  "Count" :  41  }, 
+  {  "Value" :  "201712"  ,  "Count" :  3002  }, 
+  {  "Value" :  "201801"  ,  "Count" :  29  }, 
+  {  "Value" :  "201802"  ,  "Count" :  46  }, 
+  {  "Value" :  "201803"  ,  "Count" :  321  }, 
+  {  "Value" :  "201804"  ,  "Count" :  246  }, 
+  {  "Value" :  "201805"  ,  "Count" :  265  }, 
+  {  "Value" :  "201806"  ,  "Count" :  1767  }, 
+  {  "Value" :  "201807"  ,  "Count" :  123  }, 
+  {  "Value" :  "201808"  ,  "Count" :  370  }, 
+  {  "Value" :  "201809"  ,  "Count" :  744  }, 
+  {  "Value" :  "201810"  ,  "Count" :  255  }, 
+  {  "Value" :  "201811"  ,  "Count" :  122  }, 
+  {  "Value" :  "201812"  ,  "Count" :  9298  }, 
+  {  "Value" :  "201901"  ,  "Count" :  61  }, 
+  {  "Value" :  "201902"  ,  "Count" :  49  }, 
+  {  "Value" :  "201903"  ,  "Count" :  319  }, 
+  {  "Value" :  "201904"  ,  "Count" :  162  }, 
+  {  "Value" :  "201905"  ,  "Count" :  206  }, 
+  {  "Value" :  "201906"  ,  "Count" :  1060  }, 
+  {  "Value" :  "201907"  ,  "Count" :  58  }, 
+  {  "Value" :  "201908"  ,  "Count" :  44  }, 
+  {  "Value" :  "201909"  ,  "Count" :  42  }, 
+  {  "Value" :  "201910"  ,  "Count" :  7  }
 ]</t>
   </si>
   <si>
@@ -4820,10 +4823,10 @@
         <v>29</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>29</v>
@@ -4838,7 +4841,7 @@
         <v>29</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>29</v>
@@ -4850,25 +4853,25 @@
         <v>29</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="S6" s="6" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>29</v>
@@ -4886,36 +4889,36 @@
         <v>29</v>
       </c>
       <c r="AB6" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J7" s="9" t="b">
         <v>0</v>
@@ -4924,7 +4927,7 @@
         <v>29</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>29</v>
@@ -4936,7 +4939,7 @@
         <v>29</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q7" s="8" t="s">
         <v>29</v>
@@ -4948,16 +4951,16 @@
         <v>29</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="V7" s="7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="W7" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="X7" s="7" t="n">
         <v>2</v>
@@ -4972,18 +4975,18 @@
         <v>29</v>
       </c>
       <c r="AB7" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>29</v>
@@ -4995,13 +4998,13 @@
         <v>29</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J8" s="9" t="b">
         <v>0</v>
@@ -5010,7 +5013,7 @@
         <v>29</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>29</v>
@@ -5022,7 +5025,7 @@
         <v>29</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="8" t="s">
         <v>29</v>
@@ -5034,16 +5037,16 @@
         <v>29</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="V8" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="X8" s="7" t="n">
         <v>3</v>
@@ -5058,24 +5061,24 @@
         <v>29</v>
       </c>
       <c r="AB8" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" ht="25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>29</v>
@@ -5087,7 +5090,7 @@
         <v>29</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J9" s="9" t="b">
         <v>0</v>
@@ -5096,7 +5099,7 @@
         <v>29</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M9" s="11" t="s">
         <v>29</v>
@@ -5108,7 +5111,7 @@
         <v>29</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q9" s="8" t="s">
         <v>29</v>
@@ -5120,16 +5123,16 @@
         <v>29</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="X9" s="7" t="n">
         <v>2</v>
@@ -5144,24 +5147,24 @@
         <v>29</v>
       </c>
       <c r="AB9" s="7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>29</v>
@@ -5173,7 +5176,7 @@
         <v>29</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J10" s="9" t="b">
         <v>0</v>
@@ -5182,7 +5185,7 @@
         <v>29</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M10" s="11" t="s">
         <v>29</v>
@@ -5194,7 +5197,7 @@
         <v>29</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q10" s="8" t="s">
         <v>29</v>
@@ -5206,16 +5209,16 @@
         <v>29</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="V10" s="7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="W10" s="7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="X10" s="7" t="n">
         <v>1</v>
@@ -5230,18 +5233,18 @@
         <v>29</v>
       </c>
       <c r="AB10" s="7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" ht="25" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>29</v>
@@ -5259,7 +5262,7 @@
         <v>29</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="J11" s="9" t="b">
         <v>0</v>
@@ -5292,16 +5295,16 @@
         <v>29</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="X11" s="7" t="n">
         <v>5</v>
@@ -5316,24 +5319,24 @@
         <v>29</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" ht="25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>29</v>
@@ -5345,7 +5348,7 @@
         <v>29</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J12" s="9" t="b">
         <v>0</v>
@@ -5354,7 +5357,7 @@
         <v>29</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>29</v>
@@ -5366,7 +5369,7 @@
         <v>29</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q12" s="8" t="s">
         <v>29</v>
@@ -5378,16 +5381,16 @@
         <v>29</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="W12" s="7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="X12" s="7" t="n">
         <v>4</v>
@@ -5402,36 +5405,36 @@
         <v>29</v>
       </c>
       <c r="AB12" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J13" s="9" t="b">
         <v>0</v>
@@ -5440,7 +5443,7 @@
         <v>29</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>29</v>
@@ -5452,7 +5455,7 @@
         <v>29</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q13" s="8" t="s">
         <v>29</v>
@@ -5464,16 +5467,16 @@
         <v>29</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>1</v>
@@ -5488,24 +5491,24 @@
         <v>29</v>
       </c>
       <c r="AB13" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" ht="25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>29</v>
@@ -5517,7 +5520,7 @@
         <v>29</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="J14" s="9" t="b">
         <v>0</v>
@@ -5526,7 +5529,7 @@
         <v>29</v>
       </c>
       <c r="L14" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M14" s="11" t="s">
         <v>29</v>
@@ -5538,7 +5541,7 @@
         <v>29</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q14" s="8" t="s">
         <v>29</v>
@@ -5550,16 +5553,16 @@
         <v>29</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="W14" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="X14" s="7" t="n">
         <v>1</v>
@@ -5574,24 +5577,24 @@
         <v>29</v>
       </c>
       <c r="AB14" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>29</v>
@@ -5603,7 +5606,7 @@
         <v>29</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J15" s="9" t="b">
         <v>0</v>
@@ -5612,7 +5615,7 @@
         <v>29</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>29</v>
@@ -5624,7 +5627,7 @@
         <v>29</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Q15" s="8" t="s">
         <v>29</v>
@@ -5636,16 +5639,16 @@
         <v>29</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="W15" s="7" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>1</v>
@@ -5660,24 +5663,24 @@
         <v>29</v>
       </c>
       <c r="AB15" s="7" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>29</v>
@@ -5689,7 +5692,7 @@
         <v>29</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J16" s="9" t="b">
         <v>0</v>
@@ -5698,7 +5701,7 @@
         <v>29</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>29</v>
@@ -5710,7 +5713,7 @@
         <v>29</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Q16" s="8" t="s">
         <v>29</v>
@@ -5722,16 +5725,16 @@
         <v>29</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="U16" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="V16" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="W16" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="X16" s="7" t="n">
         <v>3</v>
@@ -5746,18 +5749,18 @@
         <v>29</v>
       </c>
       <c r="AB16" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" ht="25" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>29</v>
@@ -5769,13 +5772,13 @@
         <v>29</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J17" s="9" t="b">
         <v>0</v>
@@ -5784,7 +5787,7 @@
         <v>29</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>29</v>
@@ -5796,25 +5799,25 @@
         <v>29</v>
       </c>
       <c r="P17" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q17" s="8" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="U17" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V17" s="7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="W17" s="7" t="s">
         <v>29</v>
@@ -5832,18 +5835,18 @@
         <v>29</v>
       </c>
       <c r="AB17" s="7" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>29</v>
@@ -5855,13 +5858,13 @@
         <v>29</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J18" s="9" t="b">
         <v>0</v>
@@ -5870,7 +5873,7 @@
         <v>29</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M18" s="11" t="s">
         <v>29</v>
@@ -5882,7 +5885,7 @@
         <v>29</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="8" t="s">
         <v>29</v>
@@ -5894,16 +5897,16 @@
         <v>29</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="U18" s="7" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="V18" s="7" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="W18" s="7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="X18" s="7" t="n">
         <v>11</v>
@@ -5918,36 +5921,36 @@
         <v>29</v>
       </c>
       <c r="AB18" s="7" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J19" s="9" t="b">
         <v>0</v>
@@ -5956,10 +5959,10 @@
         <v>29</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="N19" s="8" t="s">
         <v>29</v>
@@ -5968,28 +5971,28 @@
         <v>29</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="Q19" s="8" t="s">
-        <v>29</v>
+        <v>172</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="T19" s="7" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="U19" s="7" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="V19" s="7" t="s">
-        <v>167</v>
+        <v>29</v>
       </c>
       <c r="W19" s="7" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="X19" s="7" t="n">
         <v>6</v>
@@ -6004,36 +6007,36 @@
         <v>29</v>
       </c>
       <c r="AB19" s="7" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" ht="25" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="J20" s="9" t="b">
         <v>0</v>
@@ -6042,10 +6045,10 @@
         <v>29</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M20" s="11" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="N20" s="8" t="s">
         <v>29</v>
@@ -6054,28 +6057,28 @@
         <v>29</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="Q20" s="8" t="s">
-        <v>29</v>
+        <v>172</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="S20" s="6" t="s">
-        <v>29</v>
+        <v>173</v>
       </c>
       <c r="T20" s="7" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="V20" s="7" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
       <c r="W20" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="X20" s="7" t="n">
         <v>6</v>
@@ -6090,36 +6093,36 @@
         <v>29</v>
       </c>
       <c r="AB20" s="7" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="J21" s="9" t="b">
         <v>0</v>
@@ -6128,7 +6131,7 @@
         <v>29</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>29</v>
@@ -6140,28 +6143,28 @@
         <v>29</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="S21" s="6" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="U21" s="7" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="V21" s="7" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="W21" s="7" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="X21" s="7" t="n">
         <v>5</v>
@@ -6176,36 +6179,36 @@
         <v>29</v>
       </c>
       <c r="AB21" s="7" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" ht="25" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>29</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="J22" s="9" t="b">
         <v>0</v>
@@ -6214,7 +6217,7 @@
         <v>29</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>29</v>
@@ -6226,7 +6229,7 @@
         <v>29</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q22" s="8" t="s">
         <v>29</v>
@@ -6238,16 +6241,16 @@
         <v>29</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="U22" s="7" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="V22" s="7" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="W22" s="7" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="X22" s="7" t="n">
         <v>2</v>
@@ -6262,18 +6265,18 @@
         <v>29</v>
       </c>
       <c r="AB22" s="7" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>29</v>
@@ -6285,13 +6288,13 @@
         <v>29</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J23" s="9" t="b">
         <v>0</v>
@@ -6300,7 +6303,7 @@
         <v>29</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M23" s="11" t="s">
         <v>29</v>
@@ -6312,7 +6315,7 @@
         <v>29</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q23" s="8" t="s">
         <v>29</v>
@@ -6324,16 +6327,16 @@
         <v>29</v>
       </c>
       <c r="T23" s="7" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="U23" s="7" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="V23" s="7" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="W23" s="7" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="X23" s="7" t="n">
         <v>10</v>
@@ -6348,18 +6351,18 @@
         <v>29</v>
       </c>
       <c r="AB23" s="7" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" ht="25" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>29</v>
@@ -6371,13 +6374,13 @@
         <v>29</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="J24" s="9" t="b">
         <v>0</v>
@@ -6386,7 +6389,7 @@
         <v>29</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M24" s="11" t="s">
         <v>29</v>
@@ -6398,7 +6401,7 @@
         <v>29</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q24" s="8" t="s">
         <v>29</v>
@@ -6410,16 +6413,16 @@
         <v>29</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="V24" s="7" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="W24" s="7" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="X24" s="7" t="n">
         <v>11</v>
@@ -6434,18 +6437,18 @@
         <v>29</v>
       </c>
       <c r="AB24" s="7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" ht="25" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>29</v>
@@ -6457,13 +6460,13 @@
         <v>29</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="J25" s="9" t="b">
         <v>0</v>
@@ -6472,7 +6475,7 @@
         <v>29</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M25" s="11" t="s">
         <v>29</v>
@@ -6484,7 +6487,7 @@
         <v>29</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q25" s="8" t="s">
         <v>29</v>
@@ -6496,16 +6499,16 @@
         <v>29</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="W25" s="7" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="X25" s="7" t="n">
         <v>11</v>
@@ -6520,18 +6523,18 @@
         <v>29</v>
       </c>
       <c r="AB25" s="7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>29</v>
@@ -6543,13 +6546,13 @@
         <v>29</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="J26" s="9" t="b">
         <v>0</v>
@@ -6558,7 +6561,7 @@
         <v>29</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M26" s="11" t="s">
         <v>29</v>
@@ -6570,7 +6573,7 @@
         <v>29</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q26" s="8" t="s">
         <v>29</v>
@@ -6582,16 +6585,16 @@
         <v>29</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="U26" s="7" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="V26" s="7" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="W26" s="7" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="X26" s="7" t="n">
         <v>10</v>
@@ -6606,18 +6609,18 @@
         <v>29</v>
       </c>
       <c r="AB26" s="7" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>29</v>
@@ -6629,13 +6632,13 @@
         <v>29</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="J27" s="9" t="b">
         <v>0</v>
@@ -6644,7 +6647,7 @@
         <v>29</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M27" s="11" t="s">
         <v>29</v>
@@ -6656,7 +6659,7 @@
         <v>29</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q27" s="8" t="s">
         <v>29</v>
@@ -6668,16 +6671,16 @@
         <v>29</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="U27" s="7" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="V27" s="7" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="W27" s="7" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="X27" s="7" t="n">
         <v>10</v>
@@ -6692,18 +6695,18 @@
         <v>29</v>
       </c>
       <c r="AB27" s="7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" ht="25" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>29</v>
@@ -6715,13 +6718,13 @@
         <v>29</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>29</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="J28" s="9" t="b">
         <v>0</v>
@@ -6730,7 +6733,7 @@
         <v>29</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M28" s="11" t="s">
         <v>29</v>
@@ -6742,7 +6745,7 @@
         <v>29</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q28" s="8" t="s">
         <v>29</v>
@@ -6754,16 +6757,16 @@
         <v>29</v>
       </c>
       <c r="T28" s="7" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="U28" s="7" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="V28" s="7" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="W28" s="7" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="X28" s="7" t="n">
         <v>10</v>
@@ -6778,7 +6781,7 @@
         <v>29</v>
       </c>
       <c r="AB28" s="7" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
